--- a/Qubits/qubitcourses.xlsx
+++ b/Qubits/qubitcourses.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection Guide" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qubits Tracker'!$A$1:$U$257</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qubits Tracker'!$A$1:$U$277</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -189,8 +189,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="QubitsTracker" displayName="QubitsTracker" ref="A1:U257" headerRowCount="1">
-  <autoFilter ref="A1:U257"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="QubitsTracker" displayName="QubitsTracker" ref="A1:U277" headerRowCount="1">
+  <autoFilter ref="A1:U277"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Course"/>
     <tableColumn id="2" name="Qubit Questions attempted"/>
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U257"/>
+  <dimension ref="A1:U277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -696,11 +696,11 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T2" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="3">
@@ -760,11 +760,11 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T3" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="4">
@@ -822,11 +822,11 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T4" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="5">
@@ -884,11 +884,11 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T5" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="6">
@@ -948,11 +948,11 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T6" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="7">
@@ -1012,11 +1012,11 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T7" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="8">
@@ -1076,11 +1076,11 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T8" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="9">
@@ -1138,11 +1138,11 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T9" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="10">
@@ -1202,11 +1202,11 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T10" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="11">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T11" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="12">
@@ -1330,11 +1330,11 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T12" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="13">
@@ -1394,11 +1394,11 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T13" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="14">
@@ -1456,11 +1456,11 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T14" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="15">
@@ -1520,11 +1520,11 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T15" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="16">
@@ -1582,11 +1582,11 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T16" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="17">
@@ -1646,11 +1646,11 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T17" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="18">
@@ -1710,11 +1710,11 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T18" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="19">
@@ -1772,11 +1772,11 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T19" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="20">
@@ -1834,11 +1834,11 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T20" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="21">
@@ -1898,11 +1898,11 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T21" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="22">
@@ -1962,11 +1962,11 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T22" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="23">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T23" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="24">
@@ -2088,11 +2088,11 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T24" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="25">
@@ -2152,11 +2152,11 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T25" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="26">
@@ -2216,11 +2216,11 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T26" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="27">
@@ -2280,11 +2280,11 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T27" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="28">
@@ -2344,11 +2344,11 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T28" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="29">
@@ -2406,11 +2406,11 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T29" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="30">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>229 out of 247</t>
+          <t>247 out of 247</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2436,45 +2436,60 @@
         </is>
       </c>
       <c r="E30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="G30" t="n">
         <v>247</v>
       </c>
       <c r="H30" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.9271255060728745</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L30" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>46266.49226851852</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
       <c r="N30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>0.2604372469635627</v>
+        <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Most solved</t>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>SOLVED</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>HUMANISED</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T30" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="31">
@@ -2486,12 +2501,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0 out of 0</t>
+          <t>0 out of 250</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2500,18 +2515,20 @@
         </is>
       </c>
       <c r="E31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3" t="n"/>
+        <v>250</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
@@ -2523,20 +2540,20 @@
         <v>1</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Least solved</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T31" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="32">
@@ -2594,11 +2611,11 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T32" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="33">
@@ -2656,11 +2673,11 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T33" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="34">
@@ -2720,11 +2737,11 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T34" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="35">
@@ -2784,11 +2801,11 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T35" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="36">
@@ -2848,11 +2865,11 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T36" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="37">
@@ -2912,11 +2929,11 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T37" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="38">
@@ -2976,11 +2993,11 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T38" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="39">
@@ -3040,11 +3057,11 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T39" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="40">
@@ -3056,12 +3073,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>33 out of 33</t>
+          <t>0 out of 80</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3070,45 +3087,45 @@
         </is>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="4" t="n"/>
       <c r="N40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Least solved</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T40" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="41">
@@ -3168,11 +3185,11 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T41" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="42">
@@ -3232,11 +3249,11 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T42" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="43">
@@ -3294,11 +3311,11 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T43" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="44">
@@ -3358,11 +3375,11 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T44" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="45">
@@ -3422,11 +3439,11 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T45" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="46">
@@ -3486,11 +3503,11 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T46" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="47">
@@ -3548,11 +3565,11 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T47" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="48">
@@ -3612,11 +3629,11 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T48" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="49">
@@ -3676,11 +3693,11 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T49" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="50">
@@ -3740,11 +3757,11 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T50" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="51">
@@ -3802,11 +3819,11 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T51" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="52">
@@ -3866,11 +3883,11 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T52" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="53">
@@ -3882,12 +3899,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0 out of 36</t>
+          <t>36 out of 36</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3896,41 +3913,41 @@
         </is>
       </c>
       <c r="E53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G53" t="n">
         <v>36</v>
       </c>
       <c r="H53" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="4" t="n">
         <v>46255.50811342592</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>0</v>
+        <v>0.6635249518419111</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Least solved</t>
+          <t>Unavailable</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -3945,11 +3962,11 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T53" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="54">
@@ -4009,11 +4026,11 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T54" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="55">
@@ -4073,11 +4090,11 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T55" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="56">
@@ -4137,11 +4154,11 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T56" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="57">
@@ -4199,11 +4216,11 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T57" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="58">
@@ -4263,11 +4280,11 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T58" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="59">
@@ -4325,11 +4342,11 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T59" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="60">
@@ -4389,11 +4406,11 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T60" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="61">
@@ -4453,11 +4470,11 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T61" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="62">
@@ -4517,11 +4534,11 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T62" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="63">
@@ -4581,11 +4598,11 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T63" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="64">
@@ -4645,11 +4662,11 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T64" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="65">
@@ -4661,12 +4678,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>206 out of 237</t>
+          <t>237 out of 237</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4675,45 +4692,60 @@
         </is>
       </c>
       <c r="E65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="G65" t="n">
         <v>237</v>
       </c>
       <c r="H65" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.869198312236287</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="L65" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>46266.48935185185</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
       <c r="N65" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.3074008438818566</v>
+        <v>0</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Most solved</t>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>SOLVED</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>HUMANISED</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T65" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="66">
@@ -4773,11 +4805,11 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T66" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="67">
@@ -4835,11 +4867,11 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T67" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="68">
@@ -4899,11 +4931,11 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T68" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="69">
@@ -4963,11 +4995,11 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T69" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="70">
@@ -5027,11 +5059,11 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T70" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="71">
@@ -5091,11 +5123,11 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T71" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="72">
@@ -5155,11 +5187,11 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T72" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="73">
@@ -5219,11 +5251,11 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T73" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="74">
@@ -5283,11 +5315,11 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T74" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="75">
@@ -5345,11 +5377,11 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T75" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="76">
@@ -5409,11 +5441,11 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T76" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="77">
@@ -5473,11 +5505,11 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T77" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="78">
@@ -5537,11 +5569,11 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T78" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="79">
@@ -5601,11 +5633,11 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T79" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="80">
@@ -5663,11 +5695,11 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T80" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="81">
@@ -5727,11 +5759,11 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T81" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="82">
@@ -5789,11 +5821,11 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T82" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="83">
@@ -5851,11 +5883,11 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T83" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="84">
@@ -5867,12 +5899,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0 out of 0</t>
+          <t>0 out of 60</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5881,18 +5913,20 @@
         </is>
       </c>
       <c r="E84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="3" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
@@ -5904,20 +5938,20 @@
         <v>1</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Least solved</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T84" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="85">
@@ -5975,11 +6009,11 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T85" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="86">
@@ -6037,11 +6071,11 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T86" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="87">
@@ -6101,11 +6135,11 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T87" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="88">
@@ -6165,11 +6199,11 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T88" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="89">
@@ -6227,11 +6261,11 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T89" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="90">
@@ -6289,11 +6323,11 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T90" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="91">
@@ -6353,11 +6387,11 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T91" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="92">
@@ -6417,11 +6451,11 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T92" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="93">
@@ -6479,11 +6513,11 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T93" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="94">
@@ -6541,11 +6575,11 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T94" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="95">
@@ -6605,11 +6639,11 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T95" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="96">
@@ -6669,11 +6703,11 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T96" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="97">
@@ -6731,11 +6765,11 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T97" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="98">
@@ -6795,11 +6829,11 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T98" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="99">
@@ -6859,11 +6893,11 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T99" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="100">
@@ -6921,11 +6955,11 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T100" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="101">
@@ -6985,11 +7019,11 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T101" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="102">
@@ -7047,11 +7081,11 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T102" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="103">
@@ -7111,11 +7145,11 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T103" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="104">
@@ -7175,11 +7209,11 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T104" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="105">
@@ -7237,11 +7271,11 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T105" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="106">
@@ -7299,11 +7333,11 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T106" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="107">
@@ -7363,11 +7397,11 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T107" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="108">
@@ -7425,11 +7459,11 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T108" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="109">
@@ -7489,11 +7523,11 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T109" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="110">
@@ -7551,11 +7585,11 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T110" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="111">
@@ -7613,11 +7647,11 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T111" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="112">
@@ -7675,11 +7709,11 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T112" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="113">
@@ -7739,11 +7773,11 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T113" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="114">
@@ -7803,11 +7837,11 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T114" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="115">
@@ -7865,11 +7899,11 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T115" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="116">
@@ -7929,11 +7963,11 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T116" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="117">
@@ -7991,11 +8025,11 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T117" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="118">
@@ -8055,11 +8089,11 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T118" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="119">
@@ -8117,11 +8151,11 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T119" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="120">
@@ -8181,11 +8215,11 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T120" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="121">
@@ -8245,11 +8279,11 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T121" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="122">
@@ -8309,11 +8343,11 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T122" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="123">
@@ -8373,11 +8407,11 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T123" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="124">
@@ -8437,11 +8471,11 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T124" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="125">
@@ -8501,11 +8535,11 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T125" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="126">
@@ -8565,11 +8599,11 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T126" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="127">
@@ -8629,11 +8663,11 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T127" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="128">
@@ -8691,11 +8725,11 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T128" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="129">
@@ -8755,11 +8789,11 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T129" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="130">
@@ -8819,11 +8853,11 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T130" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="131">
@@ -8883,11 +8917,11 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T131" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="132">
@@ -8947,11 +8981,11 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T132" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="133">
@@ -9011,11 +9045,11 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T133" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="134">
@@ -9075,11 +9109,11 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T134" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="135">
@@ -9139,11 +9173,11 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T135" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="136">
@@ -9201,11 +9235,11 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T136" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="137">
@@ -9265,11 +9299,11 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T137" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="138">
@@ -9327,11 +9361,11 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T138" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="139">
@@ -9391,11 +9425,11 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T139" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="140">
@@ -9455,11 +9489,11 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T140" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="141">
@@ -9471,12 +9505,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0 out of 0</t>
+          <t>0 out of 120</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9485,18 +9519,20 @@
         </is>
       </c>
       <c r="E141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="3" t="n"/>
+        <v>120</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J141" t="n">
         <v>0</v>
       </c>
@@ -9508,20 +9544,20 @@
         <v>1</v>
       </c>
       <c r="O141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Least solved</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T141" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="142">
@@ -9579,11 +9615,11 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T142" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="143">
@@ -9595,12 +9631,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0 out of 0</t>
+          <t>0 out of 538</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9609,18 +9645,20 @@
         </is>
       </c>
       <c r="E143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="3" t="n"/>
+        <v>538</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J143" t="n">
         <v>0</v>
       </c>
@@ -9632,20 +9670,20 @@
         <v>1</v>
       </c>
       <c r="O143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Least solved</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T143" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="144">
@@ -9703,11 +9741,11 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T144" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="145">
@@ -9765,11 +9803,11 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T145" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="146">
@@ -9827,11 +9865,11 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T146" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="147">
@@ -9889,11 +9927,11 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T147" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="148">
@@ -9953,11 +9991,11 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T148" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="149">
@@ -10015,11 +10053,11 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T149" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="150">
@@ -10077,11 +10115,11 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T150" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="151">
@@ -10139,11 +10177,11 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T151" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="152">
@@ -10203,11 +10241,11 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T152" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="153">
@@ -10267,11 +10305,11 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T153" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="154">
@@ -10331,11 +10369,11 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T154" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="155">
@@ -10393,11 +10431,11 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T155" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="156">
@@ -10457,11 +10495,11 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T156" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="157">
@@ -10521,11 +10559,11 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T157" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="158">
@@ -10585,11 +10623,11 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T158" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="159">
@@ -10601,7 +10639,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0 out of 0</t>
+          <t>127 out of 127</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10618,24 +10656,31 @@
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
       </c>
-      <c r="I159" s="3" t="n"/>
+      <c r="I159" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K159" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L159" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L159" s="4" t="n">
+        <v>46266.49446759259</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
       <c r="N159" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O159" s="5" t="n">
         <v>0</v>
@@ -10645,13 +10690,23 @@
           <t>Unavailable</t>
         </is>
       </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>SOLVED</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>HUMANISED</t>
+        </is>
+      </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T159" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="160">
@@ -10709,11 +10764,11 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T160" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="161">
@@ -10773,11 +10828,11 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T161" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="162">
@@ -10837,11 +10892,11 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T162" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="163">
@@ -10901,11 +10956,11 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T163" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="164">
@@ -10963,13 +11018,18 @@
           <t>Most solved</t>
         </is>
       </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>ERROR_QMS</t>
+        </is>
+      </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T164" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="165">
@@ -11029,11 +11089,11 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T165" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="166">
@@ -11091,11 +11151,11 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T166" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="167">
@@ -11155,11 +11215,11 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T167" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="168">
@@ -11219,11 +11279,11 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T168" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="169">
@@ -11283,11 +11343,11 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T169" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="170">
@@ -11345,11 +11405,11 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T170" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="171">
@@ -11407,11 +11467,11 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T171" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="172">
@@ -11469,11 +11529,11 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T172" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="173">
@@ -11531,11 +11591,11 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T173" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="174">
@@ -11593,11 +11653,11 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T174" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="175">
@@ -11655,11 +11715,11 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T175" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="176">
@@ -11717,11 +11777,11 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T176" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="177">
@@ -11779,11 +11839,11 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T177" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="178">
@@ -11841,11 +11901,11 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T178" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="179">
@@ -11905,11 +11965,11 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T179" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="180">
@@ -11969,11 +12029,11 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T180" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="181">
@@ -12033,11 +12093,11 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T181" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="182">
@@ -12095,11 +12155,11 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T182" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="183">
@@ -12159,11 +12219,11 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T183" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="184">
@@ -12175,12 +12235,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0 out of 0</t>
+          <t>0 out of 350</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -12189,18 +12249,20 @@
         </is>
       </c>
       <c r="E184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" s="3" t="n"/>
+        <v>350</v>
+      </c>
+      <c r="I184" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J184" t="n">
         <v>0</v>
       </c>
@@ -12212,20 +12274,20 @@
         <v>1</v>
       </c>
       <c r="O184" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Least solved</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T184" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="185">
@@ -12283,11 +12345,11 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T185" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="186">
@@ -12347,11 +12409,11 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T186" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="187">
@@ -12411,11 +12473,11 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T187" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="188">
@@ -12473,11 +12535,11 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T188" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="189">
@@ -12535,11 +12597,11 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T189" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="190">
@@ -12599,11 +12661,11 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T190" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="191">
@@ -12663,11 +12725,11 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T191" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="192">
@@ -12727,11 +12789,11 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T192" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="193">
@@ -12791,11 +12853,11 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T193" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="194">
@@ -12853,11 +12915,11 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T194" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="195">
@@ -12915,11 +12977,11 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T195" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="196">
@@ -12977,11 +13039,11 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T196" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="197">
@@ -13041,11 +13103,11 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T197" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="198">
@@ -13105,11 +13167,11 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T198" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="199">
@@ -13169,11 +13231,11 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T199" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="200">
@@ -13233,11 +13295,11 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T200" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="201">
@@ -13297,11 +13359,11 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T201" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="202">
@@ -13361,11 +13423,11 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T202" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="203">
@@ -13425,11 +13487,11 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T203" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="204">
@@ -13489,11 +13551,11 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T204" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="205">
@@ -13553,11 +13615,11 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T205" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="206">
@@ -13615,11 +13677,11 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T206" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="207">
@@ -13679,11 +13741,11 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T207" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="208">
@@ -13743,11 +13805,11 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T208" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="209">
@@ -13805,11 +13867,11 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T209" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="210">
@@ -13869,11 +13931,11 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T210" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="211">
@@ -13933,11 +13995,11 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T211" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="212">
@@ -13949,7 +14011,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>0 out of 20</t>
+          <t>17 out of 20</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13966,42 +14028,57 @@
         <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G212" t="n">
         <v>20</v>
       </c>
       <c r="H212" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="J212" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K212" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L212" s="4" t="n"/>
+        <v>0.15</v>
+      </c>
+      <c r="L212" s="4" t="n">
+        <v>46266.48614583333</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
       <c r="N212" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O212" s="5" t="n">
-        <v>1</v>
+        <v>0.12</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Least solved</t>
+          <t>Most solved</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>SOLVED</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>HUMANISED</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T212" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="213">
@@ -14061,11 +14138,11 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T213" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="214">
@@ -14125,11 +14202,11 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T214" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="215">
@@ -14187,11 +14264,11 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T215" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="216">
@@ -14251,11 +14328,11 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T216" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="217">
@@ -14313,11 +14390,11 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T217" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="218">
@@ -14377,11 +14454,11 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T218" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="219">
@@ -14439,11 +14516,11 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T219" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="220">
@@ -14503,11 +14580,11 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T220" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="221">
@@ -14567,11 +14644,11 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T221" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="222">
@@ -14629,11 +14706,11 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T222" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="223">
@@ -14691,11 +14768,11 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T223" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="224">
@@ -14755,11 +14832,11 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T224" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="225">
@@ -14819,11 +14896,11 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T225" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="226">
@@ -14883,11 +14960,11 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T226" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="227">
@@ -14945,11 +15022,11 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T227" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="228">
@@ -15009,11 +15086,11 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T228" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="229">
@@ -15073,11 +15150,11 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T229" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="230">
@@ -15137,11 +15214,11 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T230" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="231">
@@ -15201,11 +15278,11 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T231" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="232">
@@ -15263,11 +15340,11 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T232" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="233">
@@ -15327,11 +15404,11 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T233" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="234">
@@ -15389,11 +15466,11 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T234" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="235">
@@ -15451,11 +15528,11 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T235" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="236">
@@ -15467,12 +15544,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0 out of 0</t>
+          <t>0 out of 350</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -15481,18 +15558,20 @@
         </is>
       </c>
       <c r="E236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="H236" t="n">
-        <v>0</v>
-      </c>
-      <c r="I236" s="3" t="n"/>
+        <v>350</v>
+      </c>
+      <c r="I236" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J236" t="n">
         <v>0</v>
       </c>
@@ -15504,20 +15583,20 @@
         <v>1</v>
       </c>
       <c r="O236" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Least solved</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T236" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="237">
@@ -15575,11 +15654,11 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T237" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="238">
@@ -15639,11 +15718,11 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T238" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="239">
@@ -15703,11 +15782,11 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T239" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="240">
@@ -15767,11 +15846,11 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T240" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="241">
@@ -15831,11 +15910,11 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T241" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="242">
@@ -15895,11 +15974,11 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T242" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="243">
@@ -15959,11 +16038,11 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T243" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="244">
@@ -16023,11 +16102,11 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T244" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="245">
@@ -16085,11 +16164,11 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T245" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="246">
@@ -16101,7 +16180,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>206 out of 235</t>
+          <t>230 out of 235</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -16118,42 +16197,57 @@
         <v>1</v>
       </c>
       <c r="F246" t="n">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="G246" t="n">
         <v>235</v>
       </c>
       <c r="H246" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>0.8765957446808511</v>
+        <v>0.9787234042553191</v>
       </c>
       <c r="J246" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K246" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L246" s="4" t="n"/>
+        <v>0.03</v>
+      </c>
+      <c r="L246" s="4" t="n">
+        <v>46266.48527777778</v>
+      </c>
+      <c r="M246" t="n">
+        <v>0</v>
+      </c>
       <c r="N246" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O246" s="5" t="n">
-        <v>0.3007021276595745</v>
+        <v>0.01963829787234042</v>
       </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Most solved</t>
         </is>
       </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>SOLVED</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>HUMANISED</t>
+        </is>
+      </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T246" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="247">
@@ -16213,11 +16307,11 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T247" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="248">
@@ -16275,11 +16369,11 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T248" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="249">
@@ -16339,11 +16433,11 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T249" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="250">
@@ -16403,11 +16497,11 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T250" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="251">
@@ -16467,11 +16561,11 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T251" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="252">
@@ -16531,11 +16625,11 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T252" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="253">
@@ -16593,11 +16687,11 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T253" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="254">
@@ -16609,12 +16703,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>0 out of 0</t>
+          <t>0 out of 2</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -16623,18 +16717,20 @@
         </is>
       </c>
       <c r="E254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F254" t="n">
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H254" t="n">
-        <v>0</v>
-      </c>
-      <c r="I254" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="I254" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J254" t="n">
         <v>0</v>
       </c>
@@ -16646,20 +16742,20 @@
         <v>1</v>
       </c>
       <c r="O254" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Least solved</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T254" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="255">
@@ -16671,12 +16767,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>0 out of 0</t>
+          <t>0 out of 350</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -16685,18 +16781,20 @@
         </is>
       </c>
       <c r="E255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="H255" t="n">
-        <v>0</v>
-      </c>
-      <c r="I255" s="3" t="n"/>
+        <v>350</v>
+      </c>
+      <c r="I255" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J255" t="n">
         <v>0</v>
       </c>
@@ -16708,20 +16806,20 @@
         <v>1</v>
       </c>
       <c r="O255" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Least solved</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T255" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="256">
@@ -16781,11 +16879,11 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T256" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
       </c>
     </row>
     <row r="257">
@@ -16843,16 +16941,1270 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-08-21 12:11:42</t>
+          <t>2026-09-01 13:09:49</t>
         </is>
       </c>
       <c r="T257" s="4" t="n">
-        <v>46255.50638888889</v>
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>AB-730T00: Transform business workflows with generative AI  
+Uncertified</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>0 out of 159</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E258" t="b">
+        <v>1</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>159</v>
+      </c>
+      <c r="H258" t="n">
+        <v>159</v>
+      </c>
+      <c r="I258" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L258" s="4" t="n"/>
+      <c r="N258" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O258" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Least solved</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T258" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>AB-731T00 Drive AI transformation in your organization  
+Uncertified</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>0 out of 33</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E259" t="b">
+        <v>1</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>33</v>
+      </c>
+      <c r="H259" t="n">
+        <v>33</v>
+      </c>
+      <c r="I259" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L259" s="4" t="n"/>
+      <c r="N259" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O259" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Least solved</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T259" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Advanced Oracle &amp; PostgreSQL Database Administration, High Availability and Clustering  
+Uncertified</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E260" t="b">
+        <v>0</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" s="3" t="n"/>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L260" s="4" t="n"/>
+      <c r="N260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O260" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T260" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Advanced Power BI Analytics with Azure Databricks and Tabular Editor  
+No exam</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E261" t="b">
+        <v>0</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" s="3" t="n"/>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L261" s="4" t="n"/>
+      <c r="N261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O261" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T261" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>AI Powered workflow automation and Agentic System  
+No exam</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>0 out of 60</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E262" t="b">
+        <v>1</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>60</v>
+      </c>
+      <c r="H262" t="n">
+        <v>60</v>
+      </c>
+      <c r="I262" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L262" s="4" t="n"/>
+      <c r="N262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Least solved</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T262" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Building MCP Servers for AI Applications with Azure AI Foundry &amp; VS Code  
+No exam</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E263" t="b">
+        <v>0</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" s="3" t="n"/>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L263" s="4" t="n"/>
+      <c r="N263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T263" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Certification of Capability in Business Analysis (CCBA)  
+Uncertified</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>0 out of 230</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E264" t="b">
+        <v>1</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>230</v>
+      </c>
+      <c r="H264" t="n">
+        <v>230</v>
+      </c>
+      <c r="I264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L264" s="4" t="n"/>
+      <c r="N264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O264" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Least solved</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T264" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Certified Threat Intelligence Analyst v2 (CTIA)  
+Uncertified</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>0 out of 198</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E265" t="b">
+        <v>1</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>198</v>
+      </c>
+      <c r="H265" t="n">
+        <v>198</v>
+      </c>
+      <c r="I265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L265" s="4" t="n"/>
+      <c r="N265" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Least solved</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T265" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Data Modelling Foundations for Relational Databases  
+No exam</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E266" t="b">
+        <v>0</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" s="3" t="n"/>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L266" s="4" t="n"/>
+      <c r="N266" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O266" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T266" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Data Science and Machine Learning  
+No exam</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>0 out of 276</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E267" t="b">
+        <v>1</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>276</v>
+      </c>
+      <c r="H267" t="n">
+        <v>276</v>
+      </c>
+      <c r="I267" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" s="4" t="n"/>
+      <c r="N267" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Least solved</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T267" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>DP-090T00: Implementing a Machine Learning Solution with Microsoft Azure Databricks  
+No exam</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>39 out of 42</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E268" t="b">
+        <v>1</v>
+      </c>
+      <c r="F268" t="n">
+        <v>39</v>
+      </c>
+      <c r="G268" t="n">
+        <v>42</v>
+      </c>
+      <c r="H268" t="n">
+        <v>3</v>
+      </c>
+      <c r="I268" s="3" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="J268" t="n">
+        <v>92</v>
+      </c>
+      <c r="K268" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L268" s="4" t="n"/>
+      <c r="N268" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O268" s="5" t="n">
+        <v>0.2597142857142857</v>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Most solved</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T268" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE)  
+No exam</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E269" t="b">
+        <v>0</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" s="3" t="n"/>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L269" s="4" t="n"/>
+      <c r="N269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O269" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T269" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Generative AI, Agentic AI and MCP  
+No exam</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E270" t="b">
+        <v>0</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" s="3" t="n"/>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L270" s="4" t="n"/>
+      <c r="N270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O270" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T270" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Implementing AI Solutions in Regulated Industries  
+No exam</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E271" t="b">
+        <v>0</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" s="3" t="n"/>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L271" s="4" t="n"/>
+      <c r="N271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O271" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T271" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Microsoft Foundry AI Agent Engineering Workshop  
+No exam</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E272" t="b">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" s="3" t="n"/>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L272" s="4" t="n"/>
+      <c r="N272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O272" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T272" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Oracle Autonomous AI Database Professional Workshop  
+No exam</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E273" t="b">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" s="3" t="n"/>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L273" s="4" t="n"/>
+      <c r="N273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O273" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T273" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Power BI Data Analysis for Engineers - BEL  
+No exam</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E274" t="b">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" t="n">
+        <v>0</v>
+      </c>
+      <c r="I274" s="3" t="n"/>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L274" s="4" t="n"/>
+      <c r="N274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O274" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T274" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Power BI for Finance -BEL  
+No exam</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E275" t="b">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" s="3" t="n"/>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L275" s="4" t="n"/>
+      <c r="N275" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O275" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T275" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Power Platform Functional Consultant and Power Automate _Custom  
+No exam</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E276" t="b">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" s="3" t="n"/>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L276" s="4" t="n"/>
+      <c r="N276" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O276" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T276" s="4" t="n">
+        <v>46266.54848379629</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SQL – Beyond the Basics  
+No exam</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>0 out of 0</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="E277" t="b">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I277" s="3" t="n"/>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L277" s="4" t="n"/>
+      <c r="N277" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:09:49</t>
+        </is>
+      </c>
+      <c r="T277" s="4" t="n">
+        <v>46266.54848379629</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U257"/>
-  <conditionalFormatting sqref="A2:U257">
+  <autoFilter ref="A1:U277"/>
+  <conditionalFormatting sqref="A2:U277">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$P2="Least solved"</formula>
     </cfRule>

--- a/Qubits/qubitcourses.xlsx
+++ b/Qubits/qubitcourses.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T2" s="4" t="n">
@@ -760,7 +760,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T3" s="4" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T4" s="4" t="n">
@@ -884,7 +884,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T5" s="4" t="n">
@@ -948,7 +948,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T6" s="4" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T7" s="4" t="n">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T8" s="4" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T9" s="4" t="n">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T10" s="4" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T11" s="4" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T12" s="4" t="n">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T13" s="4" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T14" s="4" t="n">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T15" s="4" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T16" s="4" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T17" s="4" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T18" s="4" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T19" s="4" t="n">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T20" s="4" t="n">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T21" s="4" t="n">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T22" s="4" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T23" s="4" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T24" s="4" t="n">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T25" s="4" t="n">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T26" s="4" t="n">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T27" s="4" t="n">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T28" s="4" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T29" s="4" t="n">
@@ -2460,10 +2460,10 @@
         <v>46266.49226851852</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0</v>
+        <v>0.09427633573609329</v>
       </c>
       <c r="O30" s="5" t="n">
         <v>0</v>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T30" s="4" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T31" s="4" t="n">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T32" s="4" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T33" s="4" t="n">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T34" s="4" t="n">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T35" s="4" t="n">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T36" s="4" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T37" s="4" t="n">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T38" s="4" t="n">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T39" s="4" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T40" s="4" t="n">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T41" s="4" t="n">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T42" s="4" t="n">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T43" s="4" t="n">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T44" s="4" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T45" s="4" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T46" s="4" t="n">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T47" s="4" t="n">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T48" s="4" t="n">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T49" s="4" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T50" s="4" t="n">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T51" s="4" t="n">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T52" s="4" t="n">
@@ -3937,10 +3937,10 @@
         <v>46255.50811342592</v>
       </c>
       <c r="M53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>0.6635249518419111</v>
+        <v>0.695246586448881</v>
       </c>
       <c r="O53" s="5" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T53" s="4" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T54" s="4" t="n">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T55" s="4" t="n">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T56" s="4" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T57" s="4" t="n">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T58" s="4" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T59" s="4" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T60" s="4" t="n">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T61" s="4" t="n">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T62" s="4" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T63" s="4" t="n">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T64" s="4" t="n">
@@ -4716,10 +4716,10 @@
         <v>46266.48935185185</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>0</v>
+        <v>0.09427633573609329</v>
       </c>
       <c r="O65" s="5" t="n">
         <v>0</v>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T65" s="4" t="n">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T66" s="4" t="n">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T67" s="4" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T68" s="4" t="n">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T69" s="4" t="n">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T70" s="4" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T71" s="4" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T72" s="4" t="n">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T73" s="4" t="n">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T74" s="4" t="n">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T75" s="4" t="n">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T76" s="4" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T77" s="4" t="n">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T78" s="4" t="n">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T79" s="4" t="n">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T80" s="4" t="n">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T81" s="4" t="n">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T82" s="4" t="n">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T83" s="4" t="n">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T84" s="4" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T85" s="4" t="n">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T86" s="4" t="n">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T87" s="4" t="n">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T88" s="4" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T89" s="4" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T90" s="4" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T91" s="4" t="n">
@@ -6437,21 +6437,36 @@
       <c r="K92" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="L92" s="4" t="n"/>
+      <c r="L92" s="4" t="n">
+        <v>46267.67987268518</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
       <c r="N92" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>0.2807941176470589</v>
+        <v>0.08079411764705882</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Most solved</t>
         </is>
       </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>SOLVED</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>HUMANISED</t>
+        </is>
+      </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T92" s="4" t="n">
@@ -6513,7 +6528,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T93" s="4" t="n">
@@ -6575,7 +6590,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T94" s="4" t="n">
@@ -6639,7 +6654,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T95" s="4" t="n">
@@ -6703,7 +6718,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T96" s="4" t="n">
@@ -6765,7 +6780,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T97" s="4" t="n">
@@ -6829,7 +6844,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T98" s="4" t="n">
@@ -6893,7 +6908,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T99" s="4" t="n">
@@ -6955,7 +6970,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T100" s="4" t="n">
@@ -7019,7 +7034,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T101" s="4" t="n">
@@ -7081,7 +7096,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T102" s="4" t="n">
@@ -7145,7 +7160,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T103" s="4" t="n">
@@ -7209,7 +7224,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T104" s="4" t="n">
@@ -7271,7 +7286,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T105" s="4" t="n">
@@ -7333,7 +7348,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T106" s="4" t="n">
@@ -7397,7 +7412,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T107" s="4" t="n">
@@ -7459,7 +7474,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T108" s="4" t="n">
@@ -7523,7 +7538,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T109" s="4" t="n">
@@ -7585,7 +7600,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T110" s="4" t="n">
@@ -7647,7 +7662,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T111" s="4" t="n">
@@ -7709,7 +7724,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T112" s="4" t="n">
@@ -7773,7 +7788,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T113" s="4" t="n">
@@ -7837,7 +7852,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T114" s="4" t="n">
@@ -7899,7 +7914,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T115" s="4" t="n">
@@ -7963,7 +7978,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T116" s="4" t="n">
@@ -8025,7 +8040,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T117" s="4" t="n">
@@ -8089,7 +8104,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T118" s="4" t="n">
@@ -8151,7 +8166,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T119" s="4" t="n">
@@ -8215,7 +8230,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T120" s="4" t="n">
@@ -8279,7 +8294,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T121" s="4" t="n">
@@ -8343,7 +8358,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T122" s="4" t="n">
@@ -8407,7 +8422,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T123" s="4" t="n">
@@ -8471,7 +8486,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T124" s="4" t="n">
@@ -8535,7 +8550,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T125" s="4" t="n">
@@ -8599,7 +8614,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T126" s="4" t="n">
@@ -8663,7 +8678,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T127" s="4" t="n">
@@ -8725,7 +8740,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T128" s="4" t="n">
@@ -8789,7 +8804,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T129" s="4" t="n">
@@ -8853,7 +8868,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T130" s="4" t="n">
@@ -8917,7 +8932,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T131" s="4" t="n">
@@ -8981,7 +8996,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T132" s="4" t="n">
@@ -9045,7 +9060,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T133" s="4" t="n">
@@ -9109,7 +9124,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T134" s="4" t="n">
@@ -9173,7 +9188,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T135" s="4" t="n">
@@ -9235,7 +9250,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T136" s="4" t="n">
@@ -9299,7 +9314,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T137" s="4" t="n">
@@ -9361,7 +9376,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T138" s="4" t="n">
@@ -9425,7 +9440,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T139" s="4" t="n">
@@ -9489,7 +9504,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T140" s="4" t="n">
@@ -9553,7 +9568,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T141" s="4" t="n">
@@ -9615,7 +9630,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T142" s="4" t="n">
@@ -9679,7 +9694,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T143" s="4" t="n">
@@ -9741,7 +9756,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T144" s="4" t="n">
@@ -9803,7 +9818,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T145" s="4" t="n">
@@ -9865,7 +9880,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T146" s="4" t="n">
@@ -9927,7 +9942,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T147" s="4" t="n">
@@ -9991,7 +10006,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T148" s="4" t="n">
@@ -10053,7 +10068,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T149" s="4" t="n">
@@ -10115,7 +10130,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T150" s="4" t="n">
@@ -10177,7 +10192,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T151" s="4" t="n">
@@ -10241,7 +10256,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T152" s="4" t="n">
@@ -10305,7 +10320,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T153" s="4" t="n">
@@ -10369,7 +10384,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T154" s="4" t="n">
@@ -10431,7 +10446,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T155" s="4" t="n">
@@ -10495,7 +10510,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T156" s="4" t="n">
@@ -10559,7 +10574,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T157" s="4" t="n">
@@ -10623,7 +10638,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T158" s="4" t="n">
@@ -10677,10 +10692,10 @@
         <v>46266.49446759259</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>0</v>
+        <v>0.09427633573609329</v>
       </c>
       <c r="O159" s="5" t="n">
         <v>0</v>
@@ -10702,7 +10717,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T159" s="4" t="n">
@@ -10764,7 +10779,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T160" s="4" t="n">
@@ -10828,7 +10843,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T161" s="4" t="n">
@@ -10892,7 +10907,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T162" s="4" t="n">
@@ -10956,7 +10971,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T163" s="4" t="n">
@@ -11025,7 +11040,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T164" s="4" t="n">
@@ -11089,7 +11104,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T165" s="4" t="n">
@@ -11151,7 +11166,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T166" s="4" t="n">
@@ -11215,7 +11230,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T167" s="4" t="n">
@@ -11279,7 +11294,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T168" s="4" t="n">
@@ -11343,7 +11358,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T169" s="4" t="n">
@@ -11405,7 +11420,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T170" s="4" t="n">
@@ -11467,7 +11482,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T171" s="4" t="n">
@@ -11529,7 +11544,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T172" s="4" t="n">
@@ -11591,7 +11606,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T173" s="4" t="n">
@@ -11653,7 +11668,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T174" s="4" t="n">
@@ -11715,7 +11730,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T175" s="4" t="n">
@@ -11777,7 +11792,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T176" s="4" t="n">
@@ -11839,7 +11854,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T177" s="4" t="n">
@@ -11901,7 +11916,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T178" s="4" t="n">
@@ -11965,7 +11980,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T179" s="4" t="n">
@@ -12029,7 +12044,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T180" s="4" t="n">
@@ -12093,7 +12108,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T181" s="4" t="n">
@@ -12155,7 +12170,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T182" s="4" t="n">
@@ -12219,7 +12234,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T183" s="4" t="n">
@@ -12283,7 +12298,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T184" s="4" t="n">
@@ -12345,7 +12360,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T185" s="4" t="n">
@@ -12409,7 +12424,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T186" s="4" t="n">
@@ -12473,7 +12488,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T187" s="4" t="n">
@@ -12535,7 +12550,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T188" s="4" t="n">
@@ -12597,7 +12612,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T189" s="4" t="n">
@@ -12661,7 +12676,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T190" s="4" t="n">
@@ -12725,7 +12740,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T191" s="4" t="n">
@@ -12789,7 +12804,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T192" s="4" t="n">
@@ -12853,7 +12868,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T193" s="4" t="n">
@@ -12915,7 +12930,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T194" s="4" t="n">
@@ -12977,7 +12992,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T195" s="4" t="n">
@@ -13039,7 +13054,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T196" s="4" t="n">
@@ -13103,7 +13118,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T197" s="4" t="n">
@@ -13167,7 +13182,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T198" s="4" t="n">
@@ -13231,7 +13246,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T199" s="4" t="n">
@@ -13295,7 +13310,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T200" s="4" t="n">
@@ -13359,7 +13374,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T201" s="4" t="n">
@@ -13423,7 +13438,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T202" s="4" t="n">
@@ -13487,7 +13502,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T203" s="4" t="n">
@@ -13551,7 +13566,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T204" s="4" t="n">
@@ -13615,7 +13630,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T205" s="4" t="n">
@@ -13677,7 +13692,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T206" s="4" t="n">
@@ -13741,7 +13756,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T207" s="4" t="n">
@@ -13805,7 +13820,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T208" s="4" t="n">
@@ -13867,7 +13882,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T209" s="4" t="n">
@@ -13931,7 +13946,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T210" s="4" t="n">
@@ -13995,7 +14010,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T211" s="4" t="n">
@@ -14049,13 +14064,13 @@
         <v>46266.48614583333</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>0</v>
+        <v>0.09427633573609329</v>
       </c>
       <c r="O212" s="5" t="n">
-        <v>0.12</v>
+        <v>0.1388552671472187</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
@@ -14074,7 +14089,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T212" s="4" t="n">
@@ -14138,7 +14153,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T213" s="4" t="n">
@@ -14202,7 +14217,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T214" s="4" t="n">
@@ -14264,7 +14279,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T215" s="4" t="n">
@@ -14328,7 +14343,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T216" s="4" t="n">
@@ -14390,7 +14405,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T217" s="4" t="n">
@@ -14454,7 +14469,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T218" s="4" t="n">
@@ -14516,7 +14531,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T219" s="4" t="n">
@@ -14580,7 +14595,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T220" s="4" t="n">
@@ -14644,7 +14659,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T221" s="4" t="n">
@@ -14706,7 +14721,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T222" s="4" t="n">
@@ -14768,7 +14783,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T223" s="4" t="n">
@@ -14832,7 +14847,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T224" s="4" t="n">
@@ -14896,7 +14911,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T225" s="4" t="n">
@@ -14960,7 +14975,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T226" s="4" t="n">
@@ -15022,7 +15037,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T227" s="4" t="n">
@@ -15086,7 +15101,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T228" s="4" t="n">
@@ -15150,7 +15165,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T229" s="4" t="n">
@@ -15214,7 +15229,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T230" s="4" t="n">
@@ -15278,7 +15293,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T231" s="4" t="n">
@@ -15340,7 +15355,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T232" s="4" t="n">
@@ -15404,7 +15419,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T233" s="4" t="n">
@@ -15466,7 +15481,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T234" s="4" t="n">
@@ -15528,7 +15543,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T235" s="4" t="n">
@@ -15592,7 +15607,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T236" s="4" t="n">
@@ -15654,7 +15669,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T237" s="4" t="n">
@@ -15718,7 +15733,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T238" s="4" t="n">
@@ -15782,7 +15797,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T239" s="4" t="n">
@@ -15846,7 +15861,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T240" s="4" t="n">
@@ -15910,7 +15925,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T241" s="4" t="n">
@@ -15974,7 +15989,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T242" s="4" t="n">
@@ -16038,7 +16053,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T243" s="4" t="n">
@@ -16102,7 +16117,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T244" s="4" t="n">
@@ -16164,7 +16179,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T245" s="4" t="n">
@@ -16218,13 +16233,13 @@
         <v>46266.48527777778</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>0</v>
+        <v>0.09427633573609329</v>
       </c>
       <c r="O246" s="5" t="n">
-        <v>0.01963829787234042</v>
+        <v>0.03849356501955908</v>
       </c>
       <c r="P246" t="inlineStr">
         <is>
@@ -16243,7 +16258,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T246" s="4" t="n">
@@ -16307,7 +16322,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T247" s="4" t="n">
@@ -16369,7 +16384,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T248" s="4" t="n">
@@ -16433,7 +16448,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T249" s="4" t="n">
@@ -16497,7 +16512,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T250" s="4" t="n">
@@ -16561,7 +16576,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T251" s="4" t="n">
@@ -16625,7 +16640,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T252" s="4" t="n">
@@ -16687,7 +16702,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T253" s="4" t="n">
@@ -16751,7 +16766,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T254" s="4" t="n">
@@ -16815,7 +16830,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T255" s="4" t="n">
@@ -16879,7 +16894,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T256" s="4" t="n">
@@ -16941,7 +16956,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T257" s="4" t="n">
@@ -17005,7 +17020,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T258" s="4" t="n">
@@ -17069,7 +17084,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T259" s="4" t="n">
@@ -17131,7 +17146,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T260" s="4" t="n">
@@ -17193,7 +17208,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T261" s="4" t="n">
@@ -17257,7 +17272,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T262" s="4" t="n">
@@ -17319,7 +17334,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T263" s="4" t="n">
@@ -17383,7 +17398,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T264" s="4" t="n">
@@ -17447,7 +17462,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T265" s="4" t="n">
@@ -17509,7 +17524,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T266" s="4" t="n">
@@ -17573,7 +17588,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T267" s="4" t="n">
@@ -17637,7 +17652,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T268" s="4" t="n">
@@ -17699,7 +17714,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T269" s="4" t="n">
@@ -17761,7 +17776,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T270" s="4" t="n">
@@ -17823,7 +17838,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T271" s="4" t="n">
@@ -17885,7 +17900,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T272" s="4" t="n">
@@ -17947,7 +17962,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T273" s="4" t="n">
@@ -18009,7 +18024,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T274" s="4" t="n">
@@ -18071,7 +18086,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T275" s="4" t="n">
@@ -18133,7 +18148,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T276" s="4" t="n">
@@ -18195,7 +18210,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>2026-09-01 13:09:49</t>
+          <t>2026-09-02 16:19:02</t>
         </is>
       </c>
       <c r="T277" s="4" t="n">
